--- a/examples/nastran_case_control.xlsx
+++ b/examples/nastran_case_control.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="HOWTO" sheetId="1" state="visible" r:id="rId1"/>
@@ -22,20 +22,42 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="FF606060"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="FF1F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
     </font>
     <font>
       <b val="1"/>
@@ -51,17 +73,8 @@
       <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Consolas"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -70,7 +83,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,79 +119,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -243,16 +246,18 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>excel_codegen</author>
+    <author>tc={00CF009F-0019-405E-9EFD-0007009200DA}</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>ANALYSIS 语句的取值（整份模型共用）；留空则这条语句也不输出
+        <t xml:space="preserve">excel_codegen:
+ANALYSIS 语句的取值（整份模型共用）；留空则这条语句也不输出
 填写位置：Global 表 B 列（所有 Case 共用）
 类型：string
 默认值：STATICS
-模板里引用：{{ analysis }}</t>
+模板里引用：{{ analysis }}
+</t>
       </text>
     </comment>
   </commentList>
@@ -262,84 +267,110 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>excel_codegen</author>
+    <author>tc={00DC0050-0061-4DCA-B702-009000330074}</author>
+    <author>tc={002900DC-00C7-42EE-B56A-00C9002300AB}</author>
+    <author>tc={004B0060-000C-4171-B73A-001700B50093}</author>
+    <author>tc={00F500CC-0071-4181-9B78-00D20067009E}</author>
+    <author>tc={0068004B-0076-4FBD-A291-0026005C00A4}</author>
+    <author>tc={006F00B1-0074-49DC-8A52-009800140099}</author>
+    <author>tc={007300E6-0000-44D5-9CBF-00A000C9002A}</author>
+    <author>tc={00CE00DE-003C-422A-B882-007000B80068}</author>
+    <author>tc={001500BE-0089-4C7B-BDB1-003D00050098}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>排序号：只用来给导出文件排序（建议 01 / 02 …），不进入生成的语句
+        <t xml:space="preserve">excel_codegen:
+排序号：只用来给导出文件排序（建议 01 / 02 …），不进入生成的语句
 填写位置：Local 表 B 列（一个 Case 一行）
 类型：string
 默认值：01
-模板里引用：{{ seq }}</t>
+模板里引用：{{ seq }}
+</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="1" shapeId="0">
       <text>
-        <t>这一行的类型：SUBCASE（普通子工况）/ SUBCOM（组合子工况）
+        <t xml:space="preserve">excel_codegen:
+这一行的类型：SUBCASE（普通子工况）/ SUBCOM（组合子工况）
 填写位置：Local 表 C 列（一个 Case 一行）
 类型：string
 约束：可选: SUBCASE / SUBCOM
 默认值：SUBCASE
-模板里引用：{{ kind }}</t>
+模板里引用：{{ kind }}
+</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="2" shapeId="0">
       <text>
-        <t>子工况编号 [i]（SUBCASE / SUBCOM 后面的整数）
+        <t xml:space="preserve">excel_codegen:
+子工况编号 [i]（SUBCASE / SUBCOM 后面的整数）
 填写位置：Local 表 D 列（一个 Case 一行）
 类型：int
 约束：范围: &gt;= 1
 默认值：1
-模板里引用：{{ subcase_id }}</t>
+模板里引用：{{ subcase_id }}
+</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="3" shapeId="0">
       <text>
-        <t>LABEL 语句；留空不输出
+        <t xml:space="preserve">excel_codegen:
+LABEL 语句；留空不输出
 填写位置：Local 表 E 列（一个 Case 一行）
 类型：string
-模板里引用：{{ label }}</t>
+模板里引用：{{ label }}
+</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="4" shapeId="0">
       <text>
-        <t>SUBTITLE 语句；留空不输出
+        <t xml:space="preserve">excel_codegen:
+SUBTITLE 语句；留空不输出
 填写位置：Local 表 F 列（一个 Case 一行）
 类型：string
-模板里引用：{{ subtitle }}</t>
+模板里引用：{{ subtitle }}
+</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="5" shapeId="0">
       <text>
-        <t>METHOD 语句（实特征值提取方法集号）；留空不输出
+        <t xml:space="preserve">excel_codegen:
+METHOD 语句（实特征值提取方法集号）；留空不输出
 填写位置：Local 表 G 列（一个 Case 一行）
 类型：string
-模板里引用：{{ method }}</t>
+模板里引用：{{ method }}
+</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="6" shapeId="0">
       <text>
-        <t>LOAD 语句（静力载荷集号）；留空不输出
+        <t xml:space="preserve">excel_codegen:
+LOAD 语句（静力载荷集号）；留空不输出
 填写位置：Local 表 H 列（一个 Case 一行）
 类型：string
-模板里引用：{{ load }}</t>
+模板里引用：{{ load }}
+</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="7" shapeId="0">
       <text>
-        <t>SPC 语句（单点约束集号）；留空不输出
+        <t xml:space="preserve">excel_codegen:
+SPC 语句（单点约束集号）；留空不输出
 填写位置：Local 表 I 列（一个 Case 一行）
 类型：string
-模板里引用：{{ spc }}</t>
+模板里引用：{{ spc }}
+</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="8" shapeId="0">
       <text>
-        <t>SUBSEQ 语句的内容，原样输出（如 1, 1.2, 1.3）；留空不输出。只有 SUBCOM 用
+        <t xml:space="preserve">excel_codegen:
+SUBSEQ 语句的内容，原样输出（如 1, 1.2, 1.3）；留空不输出。只有 SUBCOM 用
 填写位置：Local 表 J 列（一个 Case 一行）
 类型：string
-模板里引用：{{ subseq }}</t>
+模板里引用：{{ subseq }}
+</t>
       </text>
     </comment>
   </commentList>
@@ -347,7 +378,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -390,71 +421,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -462,7 +435,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -485,7 +458,7 @@
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -576,7 +549,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -598,11 +571,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
+          <a:path path="circle"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -617,230 +588,229 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:path path="circle"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:B30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>nastran_case_control.xlsx —— 参数填写与代码生成说明</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="inlineStr"/>
+      <c r="A2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>这个工作簿怎么用</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  1.  Global Parameter 的 B 列：全局变量取值（所有 Case 共用）。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  2.  Local Parameter 从第 2 行起：每个 Case 一行，下拉复制即可增加。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  3.  改完参数后回到命令行执行：</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="22" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x nastran_case_control.xlsx --write-excel</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">      只想导出代码文件就换成 --outdir &lt;目录&gt;；只预览不写回则什么参数都不加。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">      ★ 懒得开终端就双击本文件旁边的 nastran_case_control_render.bat（Windows）或跑 nastran_case_control_render.sh（Linux / macOS）。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr"/>
+      <c r="A11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>⚠  部分输出表是「快照」，不是活公式</t>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>★  部分输出表是公式（engine: excel）：改参数后 Excel 打开即重算，不用跑脚本</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   在 Excel 里改了参数、但没跑上面那条命令，输出表里的代码还是上一次的。</t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   公式支持占位符替换与行内分支（{% if %}）；要生成代码文件（--outdir）或做 CI 检查（check）仍需命令行。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">   不带 --write-excel 的 render 只预览，不会改变本文件。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr"/>
+      <c r="A15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>输出位置</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  case_control: Case Control @ B2 (horizontal)［快照·需重跑］</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  cc_summary: Summary @ B2 (vertical)［快照·需重跑］</t>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  case_control: Case Control @ B2 (horizontal)［公式·自动重算］</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  cc_summary: Summary @ B2 (vertical)［公式·自动重算］</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  Template（隐藏）：模板原文，只读参考，改它不影响渲染结果。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr"/>
+      <c r="A20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>本次生成</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  时间        2026-09-27 16:06:21</t>
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  时间        2026-09-27 17:00:43</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  输出指纹      56690080e042</t>
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  输出指纹      521a09ab1380</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  参数指纹      30cf22fabed8</t>
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  参数指纹      893a98e720ab</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  case 数    5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  cases     LC1, LC2, LC3, COMB4, LC5</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  命令      excel-codegen render -c examples/nastran_case_control.yaml -x examples/nastran_case_control.xlsx --write-excel --outdir examples/generated_nastran</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr"/>
+      <c r="A28" s="14" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>工况一览（来自上一次渲染）</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">  LC1, LC2, LC3, COMB4, LC5</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -848,8 +818,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -885,11 +854,7 @@
           <t>analysis</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>STATICS</t>
-        </is>
-      </c>
+      <c r="B2" s="9" t="n"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>ANALYSIS 语句的取值（整份模型共用）；留空则这条语句也不输出</t>
@@ -897,7 +862,9 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -905,8 +872,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -994,24 +961,22 @@
       <c r="D2" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="9" t="inlineStr"/>
+      <c r="E2" s="9" t="n"/>
       <c r="F2" s="9" t="inlineStr">
         <is>
           <t>HEAD SEA</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr"/>
-      <c r="H2" s="9" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="G2" s="9" t="n"/>
+      <c r="H2" s="9" t="n">
+        <v>1001</v>
       </c>
       <c r="I2" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr"/>
+      <c r="J2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -1032,24 +997,22 @@
       <c r="D3" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="9" t="inlineStr"/>
+      <c r="E3" s="9" t="n"/>
       <c r="F3" s="9" t="inlineStr">
         <is>
           <t>BEAM SEA</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr"/>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="n">
+        <v>1002</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr"/>
+      <c r="J3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
@@ -1085,17 +1048,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
+      <c r="H4" s="9" t="n">
+        <v>1003</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr"/>
+      <c r="J4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
@@ -1116,15 +1077,15 @@
       <c r="D5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
+      <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="inlineStr">
         <is>
           <t>COMBINED 1.0 / 1.2 / 1.3</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
-      <c r="I5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="inlineStr">
         <is>
           <t>1, 1.2, 1.3</t>
@@ -1150,23 +1111,17 @@
       <c r="D6" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="I6" s="9" t="n"/>
+      <c r="J6" s="9" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C2:C6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="取值不合规" error="kind：可选: SUBCASE / SUBCOM" promptTitle="kind" prompt="可选: SUBCASE / SUBCOM" type="list">
-      <formula1>"SUBCASE,SUBCOM"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="取值不合规" error="subcase_id：范围: &gt;= 1" promptTitle="subcase_id" prompt="范围: &gt;= 1" type="whole" operator="greaterThanOrEqual">
-      <formula1>1</formula1>
-    </dataValidation>
-  </dataValidations>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -1174,266 +1129,312 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B1:F10"/>
+  <dimension ref="B1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="160" customWidth="1" min="2" max="3"/>
+    <col width="160" customWidth="1" min="3" max="3"/>
+    <col width="160" customWidth="1" min="4" max="4"/>
+    <col width="160" customWidth="1" min="5" max="5"/>
+    <col width="160" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>LC1</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>LC2</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>LC3</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>COMB4</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>LC5</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SUBCASE 1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SUBCASE 2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SUBCASE 3</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SUBCOM 4</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SUBCASE 5</t>
-        </is>
+      <c r="B2">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SUBTITLE = HEAD SEA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>SUBTITLE = BEAM SEA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LABEL = QTR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>SUBTITLE = COMBINED 1.0 / 1.2 / 1.3</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ANALYSIS = STATICS</t>
-        </is>
+      <c r="B3">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("label",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LABEL = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("label",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("label",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LABEL = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("label",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="D3">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("label",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LABEL = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("label",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("label",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LABEL = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("label",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("label",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LABEL = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("label",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("label",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ANALYSIS = STATICS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ANALYSIS = STATICS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SUBTITLE = QUARTERING SEA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ANALYSIS = STATICS</t>
-        </is>
+      <c r="B4">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBTITLE = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C4">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBTITLE = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="D4">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBTITLE = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBTITLE = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBTITLE = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LOAD = 101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LOAD = 102</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ANALYSIS = STATICS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SUBSEQ = 1, 1.2, 1.3</t>
-        </is>
+      <c r="B5">
+        <f>IF((IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&lt;&gt;""),"ANALYSIS = "&amp;IF(ISBLANK(INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>IF((IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&lt;&gt;""),"ANALYSIS = "&amp;IF(ISBLANK(INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>IF((IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&lt;&gt;""),"ANALYSIS = "&amp;IF(ISBLANK(INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>IF((IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&lt;&gt;""),"ANALYSIS = "&amp;IF(ISBLANK(INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>IF((IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&lt;&gt;""),"ANALYSIS = "&amp;IF(ISBLANK(INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$D:$D,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$B:$B,MATCH("analysis",'Global Parameter'!$A:$A,0)))&amp;IF(ISBLANK(INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"",INDEX('Global Parameter'!$E:$E,MATCH("analysis",'Global Parameter'!$A:$A,0))),"")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SPC = 1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>SPC = 1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>METHOD = 1</t>
-        </is>
+      <c r="B6">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("method",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"METHOD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("method",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"METHOD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("method",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"METHOD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("method",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"METHOD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("method",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"METHOD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LOAD = 103</t>
-        </is>
+      <c r="B7">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("load",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LOAD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("load",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LOAD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="D7">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("load",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LOAD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("load",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LOAD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("load",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"LOAD = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>SPC = 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="B8">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("spc",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SPC = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C8">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("spc",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SPC = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="D8">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("spc",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SPC = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("spc",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SPC = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("spc",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SPC = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subseq",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBSEQ = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,2,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="C9">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subseq",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBSEQ = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,3,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="D9">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subseq",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBSEQ = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,4,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subseq",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBSEQ = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,5,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>IF((IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subseq",'Local Parameter'!$1:$1,0)))&lt;&gt;""),"SUBSEQ = "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,6,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;"","")</f>
+        <v/>
+      </c>
+    </row>
     <row r="10"/>
+    <row r="11"/>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A2:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="92" customWidth="1" min="2" max="2"/>
+    <col width="160" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>LC1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SUBCASE 1 ｜ SUBTITLE=HEAD SEA ｜ METHOD= ｜ LOAD=101 ｜ SPC=1 ｜ SUBSEQ=</t>
-        </is>
+      <c r="B2">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""&amp;" ｜ SUBTITLE="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ METHOD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ LOAD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SPC="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SUBSEQ="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$2,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;""</f>
+        <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>LC2</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SUBCASE 2 ｜ SUBTITLE=BEAM SEA ｜ METHOD= ｜ LOAD=102 ｜ SPC=1 ｜ SUBSEQ=</t>
-        </is>
+      <c r="B3">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""&amp;" ｜ SUBTITLE="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ METHOD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ LOAD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SPC="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SUBSEQ="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$3,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;""</f>
+        <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>LC3</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SUBCASE 3 ｜ SUBTITLE=QUARTERING SEA ｜ METHOD=1 ｜ LOAD=103 ｜ SPC=2 ｜ SUBSEQ=</t>
-        </is>
+      <c r="B4">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""&amp;" ｜ SUBTITLE="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ METHOD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ LOAD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SPC="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SUBSEQ="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$4,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;""</f>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>COMB4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SUBCOM 4 ｜ SUBTITLE=COMBINED 1.0 / 1.2 / 1.3 ｜ METHOD= ｜ LOAD= ｜ SPC= ｜ SUBSEQ=1, 1.2, 1.3</t>
-        </is>
+      <c r="B5">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""&amp;" ｜ SUBTITLE="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ METHOD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ LOAD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SPC="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SUBSEQ="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$5,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;""</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>LC5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SUBCASE 5 ｜ SUBTITLE= ｜ METHOD= ｜ LOAD= ｜ SPC= ｜ SUBSEQ=</t>
-        </is>
+      <c r="B6">
+        <f>""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("kind",'Local Parameter'!$1:$1,0))),"SUBCASE",IF(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("kind",'Local Parameter'!$1:$1,0))="","SUBCASE",INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("kind",'Local Parameter'!$1:$1,0))))&amp;""&amp;" "&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("subcase_id",'Local Parameter'!$1:$1,0))),1,IF(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("subcase_id",'Local Parameter'!$1:$1,0))="",1,INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("subcase_id",'Local Parameter'!$1:$1,0))))&amp;""&amp;" ｜ SUBTITLE="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("subtitle",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("subtitle",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ METHOD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("method",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("method",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ LOAD="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("load",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("load",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SPC="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("spc",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("spc",'Local Parameter'!$1:$1,0)))&amp;""&amp;" ｜ SUBSEQ="&amp;""&amp;IF(ISBLANK(INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("subseq",'Local Parameter'!$1:$1,0))),"",INDEX('Local Parameter'!$A:$ZZ,$6,MATCH("subseq",'Local Parameter'!$1:$1,0)))&amp;""</f>
+        <v/>
       </c>
     </row>
     <row r="7"/>
     <row r="8"/>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1728,7 +1729,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-27 16:06:21</t>
+          <t>2026-09-27 17:00:43</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1741,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>56690080e042</t>
+          <t>521a09ab1380</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1753,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30cf22fabed8</t>
+          <t>893a98e720ab</t>
         </is>
       </c>
     </row>
@@ -1781,6 +1782,8 @@
       </c>
     </row>
   </sheetData>
+  <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" useFirstPageNumber="0" pageOrder="downThenOver" usePrinterDefaults="1" blackAndWhite="0" draft="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </worksheet>
 </file>